--- a/data_dictionaries/en/Belvo_Data_Dictionary_en.xlsx
+++ b/data_dictionaries/en/Belvo_Data_Dictionary_en.xlsx
@@ -32102,7 +32102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -32660,17 +32660,18 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax</t>
+          <t>tax_details.retained_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>The type of retained tax (for example, ISR, IVA or IEPS).</t>
+          <t xml:space="preserve">The tax type code for this retained tax, as defined by the legal entity in the country.
+</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -32686,7 +32687,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -32695,25 +32696,25 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax_percentage</t>
+          <t>tax_details.retained_taxes[].tax</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>The percentage of tax retained.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>The type of retained tax (for example, ISR, IVA or IEPS).</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32721,7 +32722,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -32730,12 +32731,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].pre_tax_amount</t>
+          <t>tax_details.retained_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>The amount before tax.</t>
+          <t>The percentage of tax retained.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
@@ -32765,19 +32766,15 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>tax_details.retained_taxes[].tax_amount</t>
+          <t>tax_details.retained_taxes[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>The amount of retained tax.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
+          <t>The amount before tax.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>number</t>
@@ -32795,7 +32792,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -32804,21 +32801,29 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes</t>
+          <t>tax_details.retained_taxes[].tax_amount</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>List of transferred taxes.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
+          <t>The amount of retained tax.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32835,22 +32840,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax</t>
+          <t>tax_details.transferred_taxes</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>The type of transferred tax (for example, ISR, IVA or IEPS).</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>IVA</t>
-        </is>
-      </c>
+          <t>List of transferred taxes.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -32870,29 +32871,26 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax_percentage</t>
+          <t>tax_details.transferred_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>The percentage of tax transferred.</t>
+          <t xml:space="preserve">The tax type code (TipoFactor) for this transferred tax, as defined by the legal entity in the country.
+</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32900,7 +32898,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -32909,29 +32907,25 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].pre_tax_amount</t>
+          <t>tax_details.transferred_taxes[].tax</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>The amount before tax.</t>
+          <t>The type of transferred tax (for example, ISR, IVA or IEPS).</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>IVA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -32948,17 +32942,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>tax_details.transferred_taxes[].tax_amount</t>
+          <t>tax_details.transferred_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>The amount of transferred tax.</t>
+          <t>The percentage of tax transferred.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>150.4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -32987,33 +32981,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sender_id</t>
+          <t>tax_details.transferred_taxes[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>The fiscal ID of the invoice sender</t>
+          <t>The amount before tax.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>AAA111111AA11</t>
+          <t>940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -33022,25 +33020,29 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>sender_fiscal_regime</t>
+          <t>tax_details.transferred_taxes[].tax_amount</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>The tax regime of the sender, as defined by the legal entity in the country.</t>
+          <t>The amount of transferred tax.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>150.4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33048,7 +33050,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
@@ -33057,17 +33059,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>sender_name</t>
+          <t>sender_id</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The name of the invoice sender.</t>
+          <t>The fiscal ID of the invoice sender</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ACME CORP</t>
+          <t>AAA111111AA11</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -33092,10 +33094,80 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>sender_fiscal_regime</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>The tax regime of the sender, as defined by the legal entity in the country.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>sender_name</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>The name of the invoice sender.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ACME CORP</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>sender_tax_fraud_status</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicates whether or not the sender is on SAT's tax fraud list for having submitted incorrect data, having outstanding payments, or having conducted business that is in violation of the fiscal institution's regulations.&lt;br&gt;&lt;br&gt;
 SAT updates the tax fraud list every three months. &lt;br&gt;&lt;br&gt;
@@ -33119,79 +33191,9 @@
 </t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>NO_TAX_FRAUD_STATUS</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>receiver_id</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>The fiscal ID of the invoice receiver.</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>BBB222222BB22</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>receiver_postal_code</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>The postal code of the receiver.</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>11560</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -33207,7 +33209,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -33216,17 +33218,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>receiver_fiscal_regime</t>
+          <t>receiver_id</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>The tax regime of the receiver, as defined by the legal entity in the country.</t>
+          <t>The fiscal ID of the invoice receiver.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>BBB222222BB22</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -33237,7 +33239,7 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -33251,17 +33253,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>receiver_name</t>
+          <t>receiver_postal_code</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>The name of the invoice receiver.</t>
+          <t>The postal code of the receiver.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>BELVO CORP</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -33272,12 +33274,12 @@
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -33286,10 +33288,80 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>receiver_fiscal_regime</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>The tax regime of the receiver, as defined by the legal entity in the country.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>receiver_name</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>The name of the invoice receiver.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>BELVO CORP</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>receiver_tax_fraud_status</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicates whether or not the receiver is on SAT's tax fraud list for having submitted incorrect data, having outstanding payments, or having conducted business that is in violation of the fiscal institution's regulations.&lt;br&gt;&lt;br&gt;
 SAT updates the tax fraud list every three months. &lt;br&gt;&lt;br&gt;
@@ -33313,92 +33385,20 @@
 </t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>NO_TAX_FRAUD_STATUS</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>cancelation_status</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">If the invoice is cancelled, this field indicates the status of the cancellation.
-</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>cancelation_update_date</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The date of the invoice cancelation, in `YYYY-MM-DD` format.
-</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-02</t>
-        </is>
-      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -33412,30 +33412,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>certification_date</t>
+          <t>cancelation_status</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The date of the fiscal certification, in `YYYY-MM-DD` format.
-</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-01</t>
-        </is>
-      </c>
+          <t xml:space="preserve">If the invoice is cancelled, this field indicates the status of the cancellation.
+</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33452,18 +33444,18 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>certification_authority</t>
+          <t>cancelation_update_date</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The fiscal ID of the certification provider.
+          <t xml:space="preserve">The date of the invoice cancelation, in `YYYY-MM-DD` format.
 </t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CCC333333CC33</t>
+          <t>2019-12-02</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -33471,7 +33463,11 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33488,234 +33484,238 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>certification_date</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The date of the fiscal certification, in `YYYY-MM-DD` format.
+</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>certification_authority</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fiscal ID of the certification provider.
+</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CCC333333CC33</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>payment_type</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The payment type code used for this invoice, as defined by the country legal entity.
 - 🇲🇽 Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-type" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;
 </t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>payment_type_description</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">*This field has been deprecated. For more information regarding Belvo and deprecation, see our Deprecated fields explanation.*
 </t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>payment_method</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The payment method code used for this invoice, as defined by the legal entity of the country.
 - 🇲🇽 Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-method" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;. For Mexico, we return `PUE`, `PPD`, or `null`.
 </t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>PUE</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>PUE, PPD, None</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>payment_method_description</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">*This field has been deprecated. For more information regarding Belvo and deprecation, see our Deprecated fields explanation.*
 *The description of the payment method used for this invoice.*
 </t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>usage</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The invoice's usage code, as defined by the legal entity of the country. 
 - 🇲🇽 Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#usage" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;
 </t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>P01</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The CFDI version of the invoice.
-</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>place_of_issue</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The postcode of where the invoice was issued.
-</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>01165</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -33740,30 +33740,34 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>invoice_details</t>
+          <t>version</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A list of descriptions for each item (purchased product or service provided) in the invoice.
-</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The CFDI version of the invoice.
+</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -33772,18 +33776,18 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].collected_at</t>
+          <t>place_of_issue</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
+          <t xml:space="preserve">The postcode of where the invoice was issued.
 </t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>01165</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -33791,11 +33795,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -33803,7 +33803,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -33812,23 +33812,19 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].description</t>
+          <t>invoice_details</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The description of the invoice item (an invoice can have one or more items).
-</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>December 2019 accounting fees</t>
-        </is>
-      </c>
+          <t xml:space="preserve">A list of descriptions for each item (purchased product or service provided) in the invoice.
+</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -33839,7 +33835,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -33848,17 +33844,18 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].product_identification</t>
+          <t>invoice_details[].collected_at</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>The identification code of the product or the service, as defined by the legal entity in the country.\n- \U0001F1F2\U0001F1FD &lt;a href="http://200.57.3.89/Pys/catPyS.aspx" target="_blank"&gt;Mexico&lt;/a&gt;.</t>
+          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
+</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>84101600</t>
+          <t>2022-02-09T08:45:50.406032Z</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -33866,15 +33863,19 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -33883,29 +33884,26 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].quantity</t>
+          <t>invoice_details[].description</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>The quantity of this invoice item.</t>
+          <t xml:space="preserve">The description of the invoice item (an invoice can have one or more items).
+</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>December 2019 accounting fees</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33922,17 +33920,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_code</t>
+          <t>invoice_details[].product_identification</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>The unit of measure, as defined by the legal entity in the country. \n- \U0001F1F2\U0001F1FD Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;SAT catalog reference&lt;/a&gt;.</t>
+          <t>The identification code of the product or the service, as defined by the legal entity in the country.\n- \U0001F1F2\U0001F1FD &lt;a href="http://200.57.3.89/Pys/catPyS.aspx" target="_blank"&gt;Mexico&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>E48</t>
+          <t>84101600</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -33957,25 +33955,29 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_description</t>
+          <t>invoice_details[].quantity</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>The description of the item, as defined by the legal entity in the country.\n- \U0001F1F2\U0001F1FD Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;SAT catalog reference&lt;/a&gt;.</t>
+          <t>The quantity of this invoice item.</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Unidad de servicio</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -33992,29 +33994,25 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].unit_amount</t>
+          <t>invoice_details[].unit_code</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>The price of one a singular item.</t>
+          <t>The unit of measure, as defined by the legal entity in the country. \n- \U0001F1F2\U0001F1FD Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;SAT catalog reference&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>E48</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -34031,16 +34029,19 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_type</t>
+          <t>invoice_details[].unit_description</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The item's tax type.
-</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
+          <t>The description of the item, as defined by the legal entity in the country.\n- \U0001F1F2\U0001F1FD Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#unit-code" target="_blank"&gt;SAT catalog reference&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Unidad de servicio</t>
+        </is>
+      </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -34049,7 +34050,7 @@
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -34063,18 +34064,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].pre_tax_amount</t>
+          <t>invoice_details[].unit_amount</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The total price for this item before tax is applied (`quantity` x `unit_amount`).
-</t>
+          <t>The price of one a singular item.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -34103,17 +34103,18 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_percentage</t>
+          <t>invoice_details[].discount</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>The tax percentage to apply.</t>
+          <t xml:space="preserve">The discount amount applied to this invoice item.
+</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -34128,7 +34129,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -34142,33 +34143,29 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].tax_amount</t>
+          <t>invoice_details[].tax_subject_code</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The amount of tax for this invoice item (`pre_tax_amount` x `tax_percentage`).
+          <t xml:space="preserve">Indicates what tax this item is subject to, as defined by the legal entity in the country.
 </t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -34182,32 +34179,29 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].total_amount</t>
+          <t>invoice_details[].identifier_number</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>The total price for this invoice item (`pre_tax_amount` + `tax_amount`).</t>
+          <t xml:space="preserve">The identification number of the item, as defined by the seller. This can be used to identify the product or service in the seller's system.
+</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>PROD-12345</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -34221,29 +34215,38 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes</t>
+          <t>invoice_details[].pre_tax_amount</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>The retained tax on the invoice item.</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The total price for this item before tax is applied (`quantity` x `unit_amount`).
+</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -34252,38 +34255,37 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].collected_at</t>
+          <t>invoice_details[].tax_percentage</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
-</t>
+          <t>The tax percentage to apply.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>date-time</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -34292,25 +34294,30 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].tax</t>
+          <t>invoice_details[].tax_amount</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>The type of retained tax (for example, ISR, IVA or IEPS).</t>
+          <t xml:space="preserve">The amount of tax for this invoice item (`pre_tax_amount` x `tax_percentage`).
+</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -34327,17 +34334,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].tax_percentage</t>
+          <t>invoice_details[].total_amount</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>The percentage of tax retained.</t>
+          <t>The total price for this invoice item (`pre_tax_amount` + `tax_amount`).</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -34366,37 +34373,29 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].retained_taxes[].retained_tax_amount</t>
+          <t>invoice_details[].retained_taxes</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>The amount of retained tax.</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>209.79</t>
-        </is>
-      </c>
+          <t>The retained tax on the invoice item.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -34405,21 +34404,30 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes</t>
+          <t>invoice_details[].retained_taxes[].collected_at</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>The transferred taxes related to the invoice.</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
+</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -34436,18 +34444,18 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].collected_at</t>
+          <t>invoice_details[].retained_taxes[].tax_type</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
+          <t xml:space="preserve">The tax type code for this retained tax, as defined by the legal entity in the country.
 </t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>Tasa</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -34455,11 +34463,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -34467,7 +34471,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -34476,17 +34480,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].tax</t>
+          <t>invoice_details[].retained_taxes[].tax</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>The type of transferred tax (for example, ISR, IVA or IEPS).</t>
+          <t>The type of retained tax (for example, ISR, IVA or IEPS).</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IVA</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -34511,12 +34515,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].tax_percentage</t>
+          <t>invoice_details[].retained_taxes[].tax_percentage</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>The percentage of tax transferred.</t>
+          <t>The percentage of tax retained.</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -34550,12 +34554,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>invoice_details[].transferred_taxes[].transferred_tax_amount</t>
+          <t>invoice_details[].retained_taxes[].retained_tax_amount</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>The amount of transferred tax.</t>
+          <t>The amount of retained tax.</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -34589,10 +34593,230 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>invoice_details[].transferred_taxes</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>The transferred taxes related to the invoice.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].collected_at</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
+</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax_type</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tax type code for this transferred tax, as defined by the legal entity in the country.
+</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Tasa</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>The type of transferred tax (for example, ISR, IVA or IEPS).</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].tax_percentage</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>The percentage of tax transferred.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>invoice_details[].transferred_taxes[].transferred_tax_amount</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>The amount of transferred tax.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>209.79</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The currency of the invoice. For example:
  - 🇧🇷 BRL (Brazilian Real)
@@ -34602,256 +34826,25 @@
 </t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>MXN</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>subtotal_amount</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The pretax amount of this invoice (sum of each item's `pre_tax_amount`).
-</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>exchange_rate</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The exchange rate used in this invoice for the currency.
-</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>0.052</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>tax_amount</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The amount of tax for this invoice (sum of each item's `tax_amount`).
-</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>discount_amount</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The total amount discounted in this invoice.
-</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The total amount of the invoice (`subtotal_amount` + `tax_amount` - `discount_amount`)
-</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>related_invoices</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>A list of related invoices.</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -34860,28 +34853,33 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>related_invoices[].relationship_type</t>
+          <t>subtotal_amount</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>The type of relationship between this invoice and the related invoice, as defined by the legal entity in the country. For more information, see our &lt;a href="https://developers.belvo.com/docs/sat-catalogs#related-invoices" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;.</t>
+          <t xml:space="preserve">The pretax amount of this invoice (sum of each item's `pre_tax_amount`).
+</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -34895,28 +34893,33 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>related_invoices[].related_invoice_identification</t>
+          <t>exchange_rate</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>The SAT ID of the related invoice.</t>
+          <t xml:space="preserve">The exchange rate used in this invoice for the currency.
+</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>INV-123456</t>
+          <t>0.052</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -34930,22 +34933,30 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>tax_amount</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A list detailing all the invoice payments.
-</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The amount of tax for this invoice (sum of each item's `tax_amount`).
+</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -34953,7 +34964,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -34962,28 +34973,28 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>payments[].date</t>
+          <t>discount_amount</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISO-8601 timestamp when the payment was made.
+          <t xml:space="preserve">The total amount discounted in this invoice.
 </t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>2020-03-17T12:00:00.000Z</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>date-time</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -35002,47 +35013,260 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The total amount of the invoice (`subtotal_amount` + `tax_amount` - `discount_amount`)
+</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>A list of related invoices.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices[].relationship_type</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>The type of relationship between this invoice and the related invoice, as defined by the legal entity in the country. For more information, see our &lt;a href="https://developers.belvo.com/docs/sat-catalogs#related-invoices" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>related_invoices[].related_invoice_identification</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>The SAT ID of the related invoice.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>INV-123456</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A list detailing all the invoice payments.
+</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>payments[].date</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISO-8601 timestamp when the payment was made.
+</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>2020-03-17T12:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
           <t>payments[].payment_type</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Payment type code used for this invoice, as defined by the country's legal entity.
 - 🇲🇽 Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payment-type" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;
 </t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>payments[].currency</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The currency of the payment. For example:
 - 🇧🇷 BRL (Brazilian Real)
@@ -35052,229 +35276,9 @@
 </t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRL</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>payments[].exchange_rate</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The `currency` to MXN currency exchange rate when the payment was made.
-</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>payments[].amount</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The invoice amount, in the currency of the original invoice.
-</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>8000.5</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>payments[].operation_number</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The fiscal institution's internal identifier for the operation.
-</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>831840</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>payments[].beneficiary_rfc</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The fiscal ID of the payment beneficiary.
-</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>BNM840515VB1</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>payments[].beneficiary_account_number</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The bank account number of the payment beneficiary.
-</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>12343453245633</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>payments[].payer_rfc</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The fiscal ID of the payment issuer.
-</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>BKJM840515VB1</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -35299,18 +35303,18 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>payments[].payer_account_number</t>
+          <t>payments[].exchange_rate</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The bank account number of the payment issuer.
+          <t xml:space="preserve">The `currency` to MXN currency exchange rate when the payment was made.
 </t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>13343663245699</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -35335,26 +35339,30 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>payments[].payer_bank_name</t>
+          <t>payments[].amount</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The banking institution that was used by the payment issuer.
+          <t xml:space="preserve">The invoice amount, in the currency of the original invoice.
 </t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>CITI BANAMEX</t>
+          <t>8000.5</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -35371,19 +35379,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>payments[].related_documents</t>
+          <t>payments[].operation_number</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A list of all the related deferred invoices affected by the payment.
-</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The fiscal institution's internal identifier for the operation.
+</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>831840</t>
+        </is>
+      </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -35394,7 +35406,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -35403,18 +35415,18 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>payments[].related_documents[].invoice_identification</t>
+          <t>payments[].beneficiary_rfc</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The fiscal institution's unique ID for the related deferred invoice.
+          <t xml:space="preserve">The fiscal ID of the payment beneficiary.
 </t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>7EE015F3-6311-11EA-B02A-00155D014007</t>
+          <t>BNM840515VB1</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -35425,7 +35437,7 @@
       <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -35439,10 +35451,222 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>payments[].beneficiary_account_number</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The bank account number of the payment beneficiary.
+</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>12343453245633</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_rfc</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fiscal ID of the payment issuer.
+</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BKJM840515VB1</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_account_number</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The bank account number of the payment issuer.
+</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>13343663245699</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>payments[].payer_bank_name</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The banking institution that was used by the payment issuer.
+</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>CITI BANAMEX</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A list of all the related deferred invoices affected by the payment.
+</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].invoice_identification</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The fiscal institution's unique ID for the related deferred invoice.
+</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>7EE015F3-6311-11EA-B02A-00155D014007</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>payments[].related_documents[].currency</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The currency of the related invoice. For example:
 - 🇧🇷 BRL (Brazilian Real)
@@ -35452,242 +35676,14 @@
 </t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>MXN</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].payment_method</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The payment method of the related invoice.
-</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>PPD</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].partiality_number</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The payment installment number.
-</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].previous_balance</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The invoice amount before the payment.
-</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>18877.84</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].amount_paid</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The amount paid in this installment.
-</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>payments[].related_documents[].outstanding_balance</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The amount remaining to be paid.
-</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>10877.84</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>payroll</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Details regarding the payroll payment. Only applicable for payroll invoices.
-</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -35707,30 +35703,26 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>payroll.days</t>
+          <t>payments[].related_documents[].payment_method</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The number of days covered by the payment.
+          <t xml:space="preserve">The payment method of the related invoice.
 </t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>PPD</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -35747,263 +35739,259 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>payments[].related_documents[].partiality_number</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The payment installment number.
+</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].previous_balance</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The invoice amount before the payment.
+</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>18877.84</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].amount_paid</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The amount paid in this installment.
+</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>payments[].related_documents[].outstanding_balance</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The amount remaining to be paid.
+</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>10877.84</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>payroll</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Details regarding the payroll payment. Only applicable for payroll invoices.
+</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>payroll.days</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The number of days covered by the payment.
+</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
           <t>payroll.type</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The payroll type, as defined by the legal entity of the country.
 - 🇲🇽 Mexico &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-type" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;
 </t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr"/>
-      <c r="I98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>payroll.amount</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The total amount of the payroll payment.
-</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>20400.1</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>payroll.version</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The version of the payroll object.
-</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>payroll.date_from</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The start date of the payment period, in `YYYY-MM-DD` format.
-</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>payroll.date_to</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The end date of the payment period, in `YYYY-MM-DD` format.
-</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-31</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>payroll.collected_at</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
-</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>payroll.payment_date</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The payment date, in `YYYY-MM-DD` format.
-</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-16</t>
-        </is>
-      </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -36011,7 +35999,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -36020,10 +36008,246 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>payroll.amount</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The total amount of the payroll payment.
+</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>20400.1</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>payroll.version</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The version of the payroll object.
+</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>payroll.date_from</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The start date of the payment period, in `YYYY-MM-DD` format.
+</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>payroll.date_to</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The end date of the payment period, in `YYYY-MM-DD` format.
+</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-31</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>payroll.collected_at</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ISO-8601 timestamp when the data point was collected.
+</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>payroll.payment_date</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The payment date, in `YYYY-MM-DD` format.
+</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>2018-07-16</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>payroll.periodicity</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">How often the payroll payment is made.
 For Mexico's SAT, we return one of the following values:
@@ -36041,229 +36265,9 @@
 </t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>MONTHLY</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>DAILY, WEEKLY, TENTH_DAY, FOURTEENTH_DAY, FIFTEENTH_DAY, MONTHLY, BIMONTHLY, PER_TASK, COMMISSION, ONE_OFF, OTHER_PERIODICITY, null</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A breakdown of the earnings for the payroll payment.
-</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].type</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The type of income. For a full list of possible values, please see the &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-earnings-breakdown-type" target="_blank"&gt;payroll earnings breakdown type table&lt;/a&gt;.
-</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>CHRISTMAS_BONUS</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].taxable_amount</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The amount of the income that is taxable.
-</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>payroll.earnings_breakdown[].vat_free_amount</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The amount of the income that is not subject to VAT.
-</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>payroll.tax_deductions</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A breakdown of the tax deductions on the payroll payment.
-</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>payroll.tax_deductions[].type</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The type of tax deduction. For a full list of possible values, please see the &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-tax-deductions-type" target="_blank"&gt;payroll tax deductions type table&lt;/a&gt;.
-</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>UNION_FEES</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -36282,36 +36286,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>DAILY, WEEKLY, TENTH_DAY, FOURTEENTH_DAY, FIFTEENTH_DAY, MONTHLY, BIMONTHLY, PER_TASK, COMMISSION, ONE_OFF, OTHER_PERIODICITY, null</t>
+        </is>
+      </c>
       <c r="I111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>payroll.tax_deductions[].amount</t>
+          <t>payroll.earnings_breakdown</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The amount of the tax deduction.
-</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
+          <t xml:space="preserve">A breakdown of the earnings for the payroll payment.
+</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -36319,7 +36319,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -36328,19 +36328,23 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments</t>
+          <t>payroll.earnings_breakdown[].type</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A breakdown of other payments for the payroll.
-</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The type of income. For a full list of possible values, please see the &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-earnings-breakdown-type" target="_blank"&gt;payroll earnings breakdown type table&lt;/a&gt;.
+</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>CHRISTMAS_BONUS</t>
+        </is>
+      </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -36360,26 +36364,30 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments[].type</t>
+          <t>payroll.earnings_breakdown[].taxable_amount</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The type of other payment. For a full list of possible values, please see the &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-other-payments-type" target="_blank"&gt;payroll other payments type table&lt;/a&gt;.
+          <t xml:space="preserve">The amount of the income that is taxable.
 </t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EMPLOYMENT_SUBSIDY</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -36387,7 +36395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
@@ -36396,18 +36404,18 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>payroll.other_payments[].amount</t>
+          <t>payroll.earnings_breakdown[].vat_free_amount</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The amount of the other payment.
+          <t xml:space="preserve">The amount of the income that is not subject to VAT.
 </t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>1505</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -36436,23 +36444,19 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>folio</t>
+          <t>payroll.tax_deductions</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The internal control number that the taxpayer assigns to the invoice.
-</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t xml:space="preserve">A breakdown of the tax deductions on the payroll payment.
+</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -36472,17 +36476,18 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>export_type</t>
+          <t>payroll.tax_deductions[].type</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>The export type of the invoice, as defined by the legal entity in the country. For more information, see our &lt;a href="https://developers.belvo.com/docs/sat-catalogs#export-type" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;.</t>
+          <t xml:space="preserve">The type of tax deduction. For a full list of possible values, please see the &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-tax-deductions-type" target="_blank"&gt;payroll tax deductions type table&lt;/a&gt;.
+</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>UNION_FEES</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -36507,22 +36512,30 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>xml</t>
+          <t>payroll.tax_deductions[].amount</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">XML of the invoice document.
-</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The amount of the tax deduction.
+</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr"/>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -36530,7 +36543,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -36539,19 +36552,19 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>payroll.other_payments</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Object containing information about any warnings related to this invoice.
+          <t xml:space="preserve">A breakdown of other payments for the payroll.
 </t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -36571,10 +36584,257 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>payroll.other_payments[].type</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The type of other payment. For a full list of possible values, please see the &lt;a href="https://developers.belvo.com/docs/sat-catalogs#payroll-other-payments-type" target="_blank"&gt;payroll other payments type table&lt;/a&gt;.
+</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYMENT_SUBSIDY</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>payroll.other_payments[].amount</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The amount of the other payment.
+</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>folio</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The internal control number that the taxpayer assigns to the invoice.
+</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The series of the invoice, as defined by the taxpayer. This is an optional field used to group invoices.
+</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>export_type</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>The export type of the invoice, as defined by the legal entity in the country. For more information, see our &lt;a href="https://developers.belvo.com/docs/sat-catalogs#export-type" target="_blank"&gt;SAT catalog reference article&lt;/a&gt;.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>xml</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XML of the invoice document.
+</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr"/>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Object containing information about any warnings related to this invoice.
+</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
           <t>warnings.code</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The warning code. Can be one of:
   - `sat_xml_limit_reached`
@@ -36583,37 +36843,37 @@
 </t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>sat_xml_limit_reached</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>warnings.message</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The description of the warning.
 The message will depend on the warning code:
@@ -36624,7 +36884,7 @@
 </t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The daily limit for XML downloads set by SAT was reached so this invoice
 might be missing data. Please check https://tinyurl.com/yydzhy5d for more
@@ -36632,90 +36892,90 @@
 </t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>sender_blacklist_status</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">*This field has been deprecated. For more information regarding Belvo and deprecation, see our Deprecated fields explanation.*
 Please use `sender_tax_fraud_status` instead.
 </t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>receiver_blacklist_status</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">*This field has been deprecated. For more information regarding Belvo and deprecation, see our Deprecated fields explanation.*
 Please use `receiver_tax_fraud_status` instead.
 </t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_dictionaries/en/Belvo_Data_Dictionary_en.xlsx
+++ b/data_dictionaries/en/Belvo_Data_Dictionary_en.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -873,14 +873,18 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>form_fields</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>This field is **deprecated** and will be removed in a future release. Please use the `id` field instead, which is the unique identifier for the institution.</t>
+        </is>
+      </c>
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -891,7 +895,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -900,22 +904,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].name</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>The username, password, or username type field.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>username</t>
-        </is>
-      </c>
+          <t>form_fields</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -935,17 +931,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].type</t>
+          <t>form_fields[].name</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>The input type for the form field. For example, string.</t>
+          <t>The username, password, or username type field.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>username</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -970,10 +966,45 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].type</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>The input type for the form field. For example, string.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>form_fields[].label</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The label of the form field. For example:
 - Client number
@@ -982,44 +1013,9 @@
 </t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Client number</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>form_fields[].validation</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>The type of input validation used for the field.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1044,17 +1040,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].placeholder</t>
+          <t>form_fields[].validation</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>The placeholder text in the form field.</t>
+          <t>The type of input validation used for the field.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ABC333333A33</t>
+          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1079,17 +1075,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].validation_message</t>
+          <t>form_fields[].placeholder</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>The message displayed when an invalid input is provided in the form field.</t>
+          <t>The placeholder text in the form field.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Invalid client number</t>
+          <t>ABC333333A33</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1114,55 +1110,55 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].validation_message</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>The message displayed when an invalid input is provided in the form field.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Invalid client number</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>form_fields[].values</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">If the form field is for documents, the institution may require additional
 input regarding the document type.
 </t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>array</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>form_fields[].values[].code</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>The code of the document.</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1182,10 +1178,45 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].values[].code</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>The code of the document.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>form_fields[].values[].label</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The label for the field. For example:
 - Cédula de Ciudadanía
@@ -1194,44 +1225,9 @@
 </t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Cédula de Ciudadanía</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>form_fields[].values[].validation</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>The type of input validation used for the field.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1256,17 +1252,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].validation_message</t>
+          <t>form_fields[].values[].validation</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>The message displayed when an invalid input is provided in the form field.</t>
+          <t>The type of input validation used for the field.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Invalid document number</t>
+          <t>^.{1,}$</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1291,17 +1287,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>form_fields[].values[].placeholder</t>
+          <t>form_fields[].values[].validation_message</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>The placeholder text in the form field.</t>
+          <t>The message displayed when an invalid input is provided in the form field.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DEF4444908M22</t>
+          <t>Invalid document number</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1326,10 +1322,45 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>form_fields[].values[].placeholder</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>The placeholder text in the form field.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>DEF4444908M22</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>features</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The features that the institution supports. If the institution has no special features, then Belvo returns an empty array.
 Here is a list of the available features:
@@ -1337,45 +1368,10 @@
 </t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>array</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>features[].name</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>The name of the feature.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>token_required</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1395,17 +1391,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>features[].description</t>
+          <t>features[].name</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>The description of the feature.</t>
+          <t>The name of the feature.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>The institution may require a token during link creation or login</t>
+          <t>token_required</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1430,10 +1426,45 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>features[].description</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>The description of the feature.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>The institution may require a token during link creation or login</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>resources</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A list of Belvo resources that you can use with the institution. This list includes one or more of the following resources:
   - `ACCOUNTS`
@@ -1457,37 +1488,37 @@
 </t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>["ACCOUNTS", "BALANCES", "INCOMES", "OWNERS", "RECURRING_EXPENSES", "RISK_INSIGHTS", "TRANSACTIONS"]</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>integration_type</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of technology used to access the institution. We return one of the following values:
 - `credentials`: Uses Belvo's scraping technology, combined with user credentials, to perform requests.
@@ -1495,49 +1526,9 @@
 </t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>credentials</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>credentials, openfinance</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indicates whether Belvo's integration with the institution is currently active (`healthy`) or undergoing maintenance (`down`).
-</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>healthy</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1558,7 +1549,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>healthy, down</t>
+          <t>credentials, openfinance</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1566,18 +1557,23 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Information about the institution on the Open Finance environment.</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Indicates whether Belvo's integration with the institution is currently active (`healthy`) or undergoing maintenance (`down`).
+</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>healthy</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1588,31 +1584,31 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>healthy, down</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.description</t>
+          <t>openbanking_information</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>A short description of the institution on the Open Finance environment. Extracted from Open Finance regulated institutions listing.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>A 1ss Bank é uma fintech fundada em janeiro de 2020, com a missão de ajudar empresas com grandes ecossistemas a se tornarem fintechs, integrando e automatizando seus processos financeiros através de APIs e plataforma white-label.</t>
-        </is>
-      </c>
+          <t>Information about the institution on the Open Finance environment.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1632,22 +1628,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.participants</t>
+          <t>openbanking_information.description</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>List of brands' servers available from the institution in Open Finance. Extracted from Open Finance regulated institutions listing.</t>
+          <t>A short description of the institution on the Open Finance environment. Extracted from Open Finance regulated institutions listing.</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>["1ss Bank"]</t>
+          <t>A 1ss Bank é uma fintech fundada em janeiro de 2020, com a missão de ajudar empresas com grandes ecossistemas a se tornarem fintechs, integrando e automatizando seus processos financeiros através de APIs e plataforma white-label.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1667,29 +1663,25 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>openbanking_information.authorization_server_id</t>
+          <t>openbanking_information.participants</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The authorization server ID (UUID) of the institution on the Open Finance Environment.</t>
+          <t>List of brands' servers available from the institution in Open Finance. Extracted from Open Finance regulated institutions listing.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>aa18fcd3-2f0b-40b1-87db-8930b10b78b1</t>
+          <t>["1ss Bank"]</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -1702,6 +1694,45 @@
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>openbanking_information.authorization_server_id</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>The authorization server ID (UUID) of the institution on the Open Finance Environment.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>aa18fcd3-2f0b-40b1-87db-8930b10b78b1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -48441,7 +48472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -48657,17 +48688,18 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>expired_at</t>
+          <t>institution_display_name</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The ISO-8601 timestamp when the consent will expire. In the case that `undefined_consent_expiration` is `true`, this field will be `null`.</t>
+          <t xml:space="preserve">The display name of the banking institution that the consent is related to.
+</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2021-02-27T13:01:41.941Z</t>
+          <t>Mock Bank</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -48675,11 +48707,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -48696,22 +48724,23 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>undefined_consent_expiration</t>
+          <t>institution_icon_logo</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Indicated whether the consent is for an undefined period, that is, that there is no expiration for the consent.</t>
+          <t xml:space="preserve">The URL to the banking institution's logo.
+</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>https://assets.belvo.io/institutions/mockbank/logo.svg</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -48731,18 +48760,18 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>belvo_organization_name</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ISO-8601 timestamp of when the data point was created in Belvo's database.
+          <t xml:space="preserve">The name registered in Belvo of the organization that created the link.
 </t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09T08:45:50.406032Z</t>
+          <t>ACME Corporation</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -48750,11 +48779,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -48771,10 +48796,241 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>link_id</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Belvo link ID that the consent belongs to.
+</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2e5d2c5e-6b3a-4b5c-8d1e-9f0a1b2c3d4e</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>uuid</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The name provided in `consent.identification_info.name` during the initial Widget Access Token Request.
+</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Jack White</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>expired_at</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>The ISO-8601 timestamp when the consent will expire. In the case that `undefined_consent_expiration` is `true`, this field will be `null`.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2021-02-27T13:01:41.941Z</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>undefined_consent_expiration</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Indicated whether the consent is for an undefined period, that is, that there is no expiration for the consent.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>consent_duration</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The duration of the consent in days. In the case that `undefined_consent_expiration` is `true`, this field will be `null`.
+Possible values:
+- `92` (3 months)
+- `183` (6 months)
+- `275` (9 months)
+- `366` (12 months)
+</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ISO-8601 timestamp of when the data point was created in Belvo's database.
+</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09T08:45:50.406032Z</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The status of the consent in the open finance network. Can be either:
   - `AUTHORISED`: The consent is still valid for use until the `expired_at` date.
@@ -48786,224 +49042,14 @@
 </t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>AUTHORISED</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>AUTHORISED, AWAITING_AUTHORISATION_CONFIRMATION, AWAITING_AUTHORISATION, REJECTED, EXPIRED, None</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>permissions</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Details regarding the permissions attached to the consent.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>permissions.ACCOUNTS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>A list of of open banking permissions relating to accessing account information.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>["ACCOUNTS_OVERDRAFT_LIMITS_READ", "ACCOUNTS_READ", "ACCOUNTS_TRANSACTIONS_READ", "ACCOUNTS_BALANCES_READ"]</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>permissions.CREDIT_CARDS</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>A list of of open banking permissions relating to accessing credit card information.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>["CREDIT_CARDS_ACCOUNTS_LIMITS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_READ", "CREDIT_CARDS_ACCOUNTS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_READ"]</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>permissions.CREDIT_OPERATIONS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>A list of of open banking permissions relating to accessing credit product information.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>["LOANS_READ", "LOANS_WARRANTIES_READ", "LOANS_SCHEDULED_INSTALMENTS_READ", "LOANS_PAYMENTS_READ", "FINANCINGS_READ", "FINANCINGS_WARRANTIES_READ", "FINANCINGS_SCHEDULED_INSTALMENTS_READ", "FINANCINGS_PAYMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_WARRANTIES_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_SCHEDULED_INSTALMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_PAYMENTS_READ", "INVOICE_FINANCINGS_READ", "INVOICE_FINANCINGS_WARRANTIES_READ", "INVOICE_FINANCINGS_SCHEDULED_INSTALMENTS_READ", "INVOICE_FINANCINGS_PAYMENTS_READ"]</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>permissions.REGISTER</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>A list of of open banking permissions relating to accessing personal information.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>["CUSTOMERS_PERSONAL_IDENTIFICATIONS_READ", "CUSTOMERS_PERSONAL_ADITTIONALINFO_READ"]</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>permissions.RESOURCES</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>A list of functional permissions required to interact with the permissions.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>["RESOURCES_READ"]</t>
-        </is>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -49014,11 +49060,256 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>AUTHORISED, AWAITING_AUTHORISATION_CONFIRMATION, AWAITING_AUTHORISATION, REJECTED, EXPIRED, None</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>permissions</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Details regarding the permissions attached to the consent.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>permissions.ACCOUNTS</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>A list of of open banking permissions relating to accessing account information.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>["ACCOUNTS_OVERDRAFT_LIMITS_READ", "ACCOUNTS_READ", "ACCOUNTS_TRANSACTIONS_READ", "ACCOUNTS_BALANCES_READ"]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>permissions.CREDIT_CARDS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>A list of of open banking permissions relating to accessing credit card information.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>["CREDIT_CARDS_ACCOUNTS_LIMITS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_READ", "CREDIT_CARDS_ACCOUNTS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_BILLS_TRANSACTIONS_READ", "CREDIT_CARDS_ACCOUNTS_READ"]</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>permissions.CREDIT_OPERATIONS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>A list of of open banking permissions relating to accessing credit product information.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>["LOANS_READ", "LOANS_WARRANTIES_READ", "LOANS_SCHEDULED_INSTALMENTS_READ", "LOANS_PAYMENTS_READ", "FINANCINGS_READ", "FINANCINGS_WARRANTIES_READ", "FINANCINGS_SCHEDULED_INSTALMENTS_READ", "FINANCINGS_PAYMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_WARRANTIES_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_SCHEDULED_INSTALMENTS_READ", "UNARRANGED_ACCOUNTS_OVERDRAFT_PAYMENTS_READ", "INVOICE_FINANCINGS_READ", "INVOICE_FINANCINGS_WARRANTIES_READ", "INVOICE_FINANCINGS_SCHEDULED_INSTALMENTS_READ", "INVOICE_FINANCINGS_PAYMENTS_READ"]</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>permissions.REGISTER</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>A list of of open banking permissions relating to accessing personal information.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>["CUSTOMERS_PERSONAL_IDENTIFICATIONS_READ", "CUSTOMERS_PERSONAL_ADITTIONALINFO_READ"]</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>permissions.RESOURCES</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>A list of functional permissions required to interact with the permissions.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>["RESOURCES_READ"]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>permissions.INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>A list of open banking permissions relating to accessing investment information.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>["BANK_FIXED_INCOMES_READ", "CREDIT_FIXED_INCOMES_READ", "FUNDS_READ", "VARIABLE_INCOMES_READ", "TREASURE_TITLES_READ"]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_dictionaries/en/Belvo_Data_Dictionary_en.xlsx
+++ b/data_dictionaries/en/Belvo_Data_Dictionary_en.xlsx
@@ -11435,7 +11435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11697,22 +11697,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>internal_identification</t>
+          <t>days_since_extraction</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Unique ID for user according to the institution. For IMSS and ISSSTE Mexico, this is the CURP.</t>
+          <t>The number of days that have passed since the employment data was originally extracted from the institution.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BLPM951331IONVGR54</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -11732,18 +11732,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>personal_data</t>
+          <t>internal_identification</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Details regarding the personal information of the individual.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>Unique ID for user according to the institution. For IMSS and ISSSTE Mexico, this is the CURP.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BLPM951331IONVGR54</t>
+        </is>
+      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -11763,23 +11767,18 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>personal_data.official_name</t>
+          <t>personal_data</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The legal name of the individual.
-</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Bruce Banner del Torro</t>
-        </is>
-      </c>
+          <t>Details regarding the personal information of the individual.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -11790,7 +11789,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -11799,18 +11798,18 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>personal_data.first_name</t>
+          <t>personal_data.official_name</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The first name of the individual.
+          <t xml:space="preserve">The legal name of the individual.
 </t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Bruce Banner del Torro</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -11835,18 +11834,18 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>personal_data.last_name</t>
+          <t>personal_data.first_name</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The last name of the individual.
+          <t xml:space="preserve">The first name of the individual.
 </t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Banner del Torro</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -11871,18 +11870,18 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>personal_data.birth_date</t>
+          <t>personal_data.last_name</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The date of birth of the individual, in `YYYY-MM-DD` format.
+          <t xml:space="preserve">The last name of the individual.
 </t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>Banner del Torro</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -11890,11 +11889,7 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11911,21 +11906,30 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements</t>
+          <t>personal_data.birth_date</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Details regarding the benefits the individual is entitled to.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The date of birth of the individual, in `YYYY-MM-DD` format.
+</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2022-02-09</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -11933,7 +11937,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -11942,23 +11946,18 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.entitled_to_health_insurance</t>
+          <t>personal_data.entitlements</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indicates whether or not the individual is entitled to health insurance.
-</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Details regarding the benefits the individual is entitled to.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -11978,12 +11977,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.entitled_to_company_benefits</t>
+          <t>personal_data.entitlements.entitled_to_health_insurance</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indicates whether or not the individual is entitled to company benefits.
+          <t xml:space="preserve">Indicates whether or not the individual is entitled to health insurance.
 </t>
         </is>
       </c>
@@ -12014,26 +12013,26 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>personal_data.entitlements.valid_until</t>
+          <t>personal_data.entitlements.entitled_to_company_benefits</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date until when the individual is covered by health insurance and/or company benefits. If `null` the employee is currently working and no end date is required.
-</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Indicates whether or not the individual is entitled to company benefits.
+</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12041,7 +12040,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -12050,10 +12049,46 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>personal_data.entitlements.valid_until</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date until when the individual is covered by health insurance and/or company benefits. If `null` the employee is currently working and no end date is required.
+</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>personal_data.entitlements.status</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicates the employment status of the individual. We return one of the following responses:
   - `EMPLOYED`
@@ -12063,49 +12098,14 @@
 </t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>EMPLOYED</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>EMPLOYED, RETIRED, UNEMPLOYED, null</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>personal_data.document_ids</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Details regarding the individual's ID documents.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -12119,16 +12119,51 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYED, RETIRED, UNEMPLOYED, null</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>personal_data.document_ids</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Details regarding the individual's ID documents.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>personal_data.document_ids[].document_type</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The type of document related to the individual. We return one of the following values:
   - `NSS`
@@ -12137,49 +12172,9 @@
 </t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>NSS</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>NSS, CURP, RFC</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>personal_data.document_ids[].document_number</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ID document's number (as a string).
-</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>10277663582</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -12198,24 +12193,28 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>NSS, CURP, RFC</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>personal_data.email</t>
+          <t>personal_data.document_ids[].document_number</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The email address of the individual.
+          <t xml:space="preserve">The ID document's number (as a string).
 </t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>bruce.banner@avengers.com</t>
+          <t>10277663582</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -12240,63 +12239,59 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>personal_data.email</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The email address of the individual.
+</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>bruce.banner@avengers.com</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>social_security_summary</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Details regarding the individual's social security contributions, according to the IMSS.
 &gt;**Note**: For ISSSTE Mexico, this value will return `null`.
 </t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>social_security_summary.weeks_redeemed</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number of weeks the individual needed to take out of their pension.
-</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12313,12 +12308,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>social_security_summary.weeks_reinstated</t>
+          <t>social_security_summary.weeks_redeemed</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of weeks the individual has paid back into their pension (*AFORE*), after having redeemed them previously.
+          <t xml:space="preserve">Number of weeks the individual needed to take out of their pension.
 </t>
         </is>
       </c>
@@ -12353,18 +12348,18 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>social_security_summary.weeks_contributed</t>
+          <t>social_security_summary.weeks_reinstated</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Number of weeks the individual has contributed to their social security, based on the number of weeks the individual has worked according to IMSS.
+          <t xml:space="preserve">Number of weeks the individual has paid back into their pension (*AFORE*), after having redeemed them previously.
 </t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -12393,21 +12388,30 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>employment_records</t>
+          <t>social_security_summary.weeks_contributed</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Details regarding the individual's employment history.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Number of weeks the individual has contributed to their social security, based on the number of weeks the individual has worked according to IMSS.
+</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12415,7 +12419,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -12424,29 +12428,21 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>employment_records[].collected_at</t>
+          <t>employment_records</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>The ISO-8601 timestamp when the data point was collected.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2020-04-23T21:32:55.336854+00:00</t>
-        </is>
-      </c>
+          <t>Details regarding the individual's employment history.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>date-time</t>
-        </is>
-      </c>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12463,104 +12459,103 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].collected_at</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>The ISO-8601 timestamp when the data point was collected.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2020-04-23T21:32:55.336854+00:00</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>date-time</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].employer</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The official name of the employer.
 &gt;**Note**: For ISSSTE Mexico, this is the official name of the entity along with the entity that is responsible for managing the employee's information, separated by a semicolon (`;`). For example: SECRETARIA DE EDUCACION PUBLICA (SEP);SECRETARIA DE EDUCACION PUBLICA (SEP).
 </t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Batman Enterprises CDMX</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>employment_records[].employer_id</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The official ID of the employer, according to the country.
 &gt;**Note**: For ISSSTE Mexico, this value will return `null`.
 </t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>780-BAT-88769-CDMX</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].start_date</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date when employment started, in `YYYY-MM-DD` format.
-</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12568,7 +12563,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -12577,71 +12572,71 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].start_date</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date when employment started, in `YYYY-MM-DD` format.
+</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2019-10-10</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].end_date</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Date when employment finished, in `YYYY-MM-DD` format.
 &gt;**Note**: This field will return `null` for the user's current employment.
 </t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>2019-12-31</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].weeks_employed</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number of weeks that the individual was employed.
-</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12649,7 +12644,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -12658,47 +12653,87 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].weeks_employed</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of weeks that the individual was employed.
+</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].state</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">In what geographical state the individual was employed, according to the country.
 &gt;**Note**: For ISSSTE Mexico, this value will return `null`.
 </t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>DISTRITO FEDERAL</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>employment_records[].most_recent_base_salary</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The most recent base salary the individual earned.
 - For IMSS Mexico, this value is calculated including the perks that the individual is entitled to throughout the year.
@@ -12706,41 +12741,41 @@
 </t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>762.54</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>employment_records[].monthly_salary</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The monthly salary of the individual, including any additional perks.
 - For IMSS Mexico, this value is calculated including the perks that the individual is entitled to throughout the year.
@@ -12748,57 +12783,21 @@
 </t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>23193.925</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].currency</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The three-letter currency code in which the salary is paid.
-</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>MXN</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -12815,18 +12814,23 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>employment_records[].employment_status_updates</t>
+          <t>employment_records[].currency</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Details regarding any employment changes of the individual.</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t xml:space="preserve">The three-letter currency code in which the salary is paid.
+</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -12837,7 +12841,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -12846,10 +12850,41 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].employment_status_updates</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Details regarding any employment changes of the individual.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>employment_records[].employment_status_updates[].event</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">For IMSS Mexico, this is the event that caused the change in employment status or salary. We return one of the following values:
   - `DISMISSED_RESIGNED`: The employee was either dismissed or resigned.
@@ -12865,41 +12900,41 @@
 </t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>HIRED</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>DISMISSED_RESIGNED, SALARY_MODIFICATION, HIRED, VOLUNTARY_CONTRIBUTION, ABSENCE, SICK_LEAVE, NORMAL, BDUTA_CERTIFICATE, DYE_CERTIFICATE</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>employment_records[].employment_status_updates[].base_salary</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The base salary of the individual, current as of the `update_date`.
   - For IMSS Mexico, this value is calculated including the perks that the individual is entitled to throughout the year.
@@ -12907,59 +12942,19 @@
 </t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>1033.09</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>float</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>employment_records[].employment_status_updates[].update_date</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The date that the employment event occurred, in `YYYY-MM-DD` format.
-</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>date</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -12978,10 +12973,50 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>employment_records[].employment_status_updates[].update_date</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The date that the employment event occurred, in `YYYY-MM-DD` format.
+</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>employment_scores</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">An array of `employment_record` scores. Each score provides an insight into employability and income generation potential in a given period.
 &gt; **Note 1**: This field is only available for links created with Mexico's IMSS. For other institutions, this field will return `null`.
@@ -12989,37 +13024,37 @@
 </t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>[{"score": 722, "period": 3, "version": "1.0.0"}, {"score": 612, "period": 6, "version": "1.0.0"}, {"score": 570, "period": 12, "version": "1.0.0"}]</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>array</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>employment_scores[].score</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">A score between 300 and 900 that provides an insight into employability and income generation potential.
 - A low score (closer to 300) could indicate lower predicted employability and income generation potential, suggesting potential challenges in securing employment or achieving higher income levels in the future.
@@ -13028,37 +13063,37 @@
 </t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>employment_scores[].period</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The number of months (in the future) that the score is calculated for.
 For example, a period of `6` indicates that the score is calculated for the next `6` months.
@@ -13066,49 +13101,14 @@
 </t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>integer</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>employment_scores[].version</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>The version of our employment score model used to perform the calculation.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -13128,18 +13128,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>files</t>
+          <t>employment_scores[].version</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Additional PDF binary files relating to the individual's employment.</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
+          <t>The version of our employment score model used to perform the calculation.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -13150,7 +13154,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -13159,23 +13163,20 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>files[].type</t>
+          <t>salary_estimation</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The title of the document.
-</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>ReporteSemanasCotizadas_190123</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Provides a modeled estimation of the user's current base salary and employment status. 
+&gt; **Note**: This field is only available for links created with Mexico's IMSS. For other institutions (such as ISSSTE), this field will return `null`.
+</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>object</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -13186,7 +13187,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -13195,38 +13196,214 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>salary_estimation.employment_status_estimate</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Current employment status estimated using an employment record with a past report date. Returns `"EMPLOYED"` (if the `base_salary_estimate` is greater than 0) or `"UNEMPLOYED"`.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EMPLOYED</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>salary_estimation.base_salary_estimate</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Current base salary (daily amount) estimated using an employment record with a past report date.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>salary_estimation.currency</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>The three-letter currency code (ISO-4217). For example, `"MXN"`.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Additional PDF binary files relating to the individual's employment.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>files[].type</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The title of the document.
+</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>ReporteSemanasCotizadas_190123</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>files[].value</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The PDF binary of the file (as a string).
 &gt; **Note**: In our sandbox environment, this field will return `null`.
 </t>
         </is>
       </c>
-      <c r="C47" s="2">
+      <c r="C52" s="2">
         <f>PDF_BINARY=</f>
         <v/>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
